--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60985769-8438-4FBF-8B58-57DD9212817D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FE3476-AF8F-43A2-9B48-71E48EEC8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000000000"/>
-    <numFmt numFmtId="174" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -216,7 +216,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FE3476-AF8F-43A2-9B48-71E48EEC8DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA24BFE2-804E-4B19-A53F-6BAAB4B2BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>address</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>CL 9 B SUR 79 A 121</t>
+  </si>
+  <si>
+    <t>CL 9 SUR 79 A 72</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -792,6 +795,20 @@
         <v>11</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>6.2029779348074401</v>
+      </c>
+      <c r="C19">
+        <v>-75.599669298243597</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA24BFE2-804E-4B19-A53F-6BAAB4B2BBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A58BC0-8D47-4AEB-9FC4-10DEDFF857F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>address</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>CL 9 SUR 79 A 72</t>
+  </si>
+  <si>
+    <t>CR 81 7 48</t>
   </si>
 </sst>
 </file>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -809,6 +812,20 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>6.2193486483621996</v>
+      </c>
+      <c r="C20">
+        <v>-75.602517023266003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A58BC0-8D47-4AEB-9FC4-10DEDFF857F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD4451E-5B3E-4C79-8FF0-EA5983053B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="4092" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -76,12 +76,86 @@
         </r>
       </text>
     </comment>
+    <comment ref="A24" authorId="0" shapeId="0" xr:uid="{5FF24EF6-8C82-4608-9ABF-1003E4671958}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Son el mismo lugar llamado Aldea de Riobamba</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{D78C3805-862C-408D-B032-329B78B81243}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ESTADISTICA:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Son el mismo lugar llamado Aldea de Riobamba
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0" xr:uid="{D0CB4A6F-0D22-4F84-9091-2FBBCCDF0FE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ESTADISTICA:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+A la dirección le falta la letra A luego de la 43
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>address</t>
   </si>
@@ -156,18 +230,119 @@
   </si>
   <si>
     <t>CR 81 7 48</t>
+  </si>
+  <si>
+    <t>CR 75 DA 2 B SUR 320</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>CR 39 A 61 B SUR 74</t>
+  </si>
+  <si>
+    <t>Sabaneta</t>
+  </si>
+  <si>
+    <t>CR 35 75 SUR 41</t>
+  </si>
+  <si>
+    <t>CR 43 C 4 SUR 143</t>
+  </si>
+  <si>
+    <t>Poblado</t>
+  </si>
+  <si>
+    <t>CR 48 4 SUR 200</t>
+  </si>
+  <si>
+    <t>CR 42 5 SUR 105</t>
+  </si>
+  <si>
+    <t>CR 45 1 59</t>
+  </si>
+  <si>
+    <t>CL 1 35 388</t>
+  </si>
+  <si>
+    <t>CR 30 2 70</t>
+  </si>
+  <si>
+    <t>CR 37 A 29 72</t>
+  </si>
+  <si>
+    <t>CL 19 43 G 80</t>
+  </si>
+  <si>
+    <r>
+      <t>CR 43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 32 39</t>
+    </r>
+  </si>
+  <si>
+    <t>CL 5 SUR 25 233</t>
+  </si>
+  <si>
+    <t>CL 28 31 19</t>
+  </si>
+  <si>
+    <r>
+      <t>CL 5 S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 25 233</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00000000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +369,26 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -215,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -223,6 +418,18 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,13 +744,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -770,7 +978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -784,7 +992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -798,7 +1006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -812,7 +1020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -824,6 +1032,225 @@
       </c>
       <c r="D20" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="7">
+        <v>6.2055100000000003</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-75.599310000000003</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="9">
+        <v>6.1506690819802801</v>
+      </c>
+      <c r="C22">
+        <v>-75.605539089698993</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>6.1431049230803803</v>
+      </c>
+      <c r="C23">
+        <v>-75.614027116736594</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="10">
+        <v>6.2003656647582499</v>
+      </c>
+      <c r="C24">
+        <v>-75.576072516427004</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>6.2012206869961499</v>
+      </c>
+      <c r="C25">
+        <v>-75.577266796531006</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>6.1978684312551797</v>
+      </c>
+      <c r="C26">
+        <v>-75.572815065978205</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>6.2054757571363997</v>
+      </c>
+      <c r="C27">
+        <v>-75.575148760836896</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
+        <v>6.2029440967304703</v>
+      </c>
+      <c r="C28">
+        <v>-75.569805556183596</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>6.1998339078687801</v>
+      </c>
+      <c r="C29">
+        <v>-75.562710064096905</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <v>6.2325358425078896</v>
+      </c>
+      <c r="C30">
+        <v>-75.569802118212607</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="11">
+        <v>6.2283366361338999</v>
+      </c>
+      <c r="C31">
+        <v>-75.564789821177598</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="11">
+        <v>6.2220457226222203</v>
+      </c>
+      <c r="C32">
+        <v>-75.573503565057194</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="11">
+        <v>6.1932089660288696</v>
+      </c>
+      <c r="C33">
+        <v>-75.562406723559306</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="11">
+        <v>6.2255598265081904</v>
+      </c>
+      <c r="C34">
+        <v>-75.560795728534899</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="12">
+        <v>6.1931741895951999</v>
+      </c>
+      <c r="C35">
+        <v>-75.5623997347966</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Inmuebles Arrendados\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD4451E-5B3E-4C79-8FF0-EA5983053B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2502CA64-C080-47B7-BFDD-017CEEFF6D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="4092" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
   <si>
     <t>address</t>
   </si>
@@ -233,9 +233,6 @@
   </si>
   <si>
     <t>CR 75 DA 2 B SUR 320</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>CR 39 A 61 B SUR 74</t>
@@ -305,42 +302,61 @@
     <t>CL 28 31 19</t>
   </si>
   <si>
-    <r>
-      <t>CL 5 S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>UR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 25 233</t>
-    </r>
+    <t>CR 9 A 20 SUR 40</t>
+  </si>
+  <si>
+    <t>CR 44 18 56</t>
+  </si>
+  <si>
+    <t>CR 31 19 445</t>
+  </si>
+  <si>
+    <t>CL 27 40 46</t>
+  </si>
+  <si>
+    <t>CL 19 43 G 155</t>
+  </si>
+  <si>
+    <t>CR 35 19 620</t>
+  </si>
+  <si>
+    <t>CL 2 SUR 20 185</t>
+  </si>
+  <si>
+    <t>CR 20 20 SUR 44</t>
+  </si>
+  <si>
+    <t>CL 4 SUR 43 AA 30</t>
+  </si>
+  <si>
+    <t>TV 38 AA 57 110</t>
+  </si>
+  <si>
+    <t>Bello</t>
+  </si>
+  <si>
+    <t>CR 67 B 51 A 72</t>
+  </si>
+  <si>
+    <t>Colores</t>
+  </si>
+  <si>
+    <t>CL 49 A 78 A 39</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
-    <numFmt numFmtId="176" formatCode="#,##0.000000000"/>
-    <numFmt numFmtId="177" formatCode="#,##0.0000000000"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000000000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00000000000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00000000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -354,7 +370,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -410,10 +426,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -424,12 +439,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -800,10 +817,10 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>6.15725127318004</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>-75.573310388030606</v>
       </c>
       <c r="D4" t="s">
@@ -814,10 +831,10 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>6.16275</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>-75.573409999999996</v>
       </c>
       <c r="D5" t="s">
@@ -832,7 +849,7 @@
         <v>6.1518899999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>-7556399</v>
+        <v>-75.563990000000004</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -870,10 +887,10 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>6.2499514794725703</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>-75.604270005408395</v>
       </c>
       <c r="D9" t="s">
@@ -1038,37 +1055,34 @@
       <c r="A21" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>6.2055100000000003</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>-75.599310000000003</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="9">
+        <v>26</v>
+      </c>
+      <c r="B22" s="8">
         <v>6.1506690819802801</v>
       </c>
       <c r="C22">
         <v>-75.605539089698993</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>6.1431049230803803</v>
@@ -1077,26 +1091,26 @@
         <v>-75.614027116736594</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="10">
+        <v>29</v>
+      </c>
+      <c r="B24" s="9">
         <v>6.2003656647582499</v>
       </c>
       <c r="C24">
         <v>-75.576072516427004</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>6.2012206869961499</v>
@@ -1105,12 +1119,12 @@
         <v>-75.577266796531006</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>6.1978684312551797</v>
@@ -1119,12 +1133,12 @@
         <v>-75.572815065978205</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>6.2054757571363997</v>
@@ -1133,12 +1147,12 @@
         <v>-75.575148760836896</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28">
         <v>6.2029440967304703</v>
@@ -1147,12 +1161,12 @@
         <v>-75.569805556183596</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29">
         <v>6.1998339078687801</v>
@@ -1161,12 +1175,12 @@
         <v>-75.562710064096905</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>6.2325358425078896</v>
@@ -1175,82 +1189,274 @@
         <v>-75.569802118212607</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="11">
+        <v>36</v>
+      </c>
+      <c r="B31" s="10">
         <v>6.2283366361338999</v>
       </c>
       <c r="C31">
         <v>-75.564789821177598</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="11">
+        <v>37</v>
+      </c>
+      <c r="B32" s="10">
         <v>6.2220457226222203</v>
       </c>
       <c r="C32">
         <v>-75.573503565057194</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="11">
+        <v>39</v>
+      </c>
+      <c r="B33" s="10">
         <v>6.1932089660288696</v>
       </c>
       <c r="C33">
         <v>-75.562406723559306</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="11">
+        <v>40</v>
+      </c>
+      <c r="B34" s="10">
         <v>6.2255598265081904</v>
       </c>
       <c r="C34">
         <v>-75.560795728534899</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="12">
+        <v>39</v>
+      </c>
+      <c r="B35" s="11">
         <v>6.1931741895951999</v>
       </c>
       <c r="C35">
         <v>-75.5623997347966</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="13">
+        <v>6.2343488581450099</v>
+      </c>
+      <c r="C36">
+        <f>-75.5362795613352</f>
+        <v>-75.536279561335206</v>
+      </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>6.2202944163771496</v>
+      </c>
+      <c r="C37">
+        <v>-75.574662687365702</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="2">
+        <v>6.22431</v>
+      </c>
+      <c r="C38" s="12">
+        <v>-75.561790000000002</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="13">
+        <v>6.2220538043196596</v>
+      </c>
+      <c r="C39">
+        <v>-75.5734705647412</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="13">
+        <v>6.22560478153442</v>
+      </c>
+      <c r="C40">
+        <v>-75.566973612531797</v>
+      </c>
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
+        <v>6.2218313180514802</v>
+      </c>
+      <c r="C41">
+        <v>-75.574244689796203</v>
+      </c>
+      <c r="D41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42">
+        <v>6.2255530668247303</v>
+      </c>
+      <c r="C42">
+        <v>-75.562572653812296</v>
+      </c>
+      <c r="D42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43">
+        <v>6.1948689974301603</v>
+      </c>
+      <c r="C43">
+        <v>-75.556969341093307</v>
+      </c>
+      <c r="D43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>6.2255980917086404</v>
+      </c>
+      <c r="C44">
+        <v>-75.566973298535501</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45">
+        <v>6.1775180853905196</v>
+      </c>
+      <c r="C45">
+        <v>-75.560908648002595</v>
+      </c>
+      <c r="D45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46">
+        <v>6.2006567972248199</v>
+      </c>
+      <c r="C46">
+        <v>-75.573747976820798</v>
+      </c>
+      <c r="D46" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47">
+        <v>6.2584312600000001</v>
+      </c>
+      <c r="C47">
+        <v>-75.583113519999998</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48">
+        <v>6.2614499349999999</v>
+      </c>
+      <c r="C48">
+        <v>-75.59603568</v>
+      </c>
+      <c r="D48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="10">
+        <v>6.3260569198161596</v>
+      </c>
+      <c r="C49">
+        <v>-75.565799612624602</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2502CA64-C080-47B7-BFDD-017CEEFF6D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8F3C82-B9B8-4684-AF65-B93CF2DDD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6108" yWindow="3744" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>address</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>CL 49 A 78 A 39</t>
+  </si>
+  <si>
+    <t>CR 115 A 64 CC 4</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1459,6 +1462,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="10">
+        <v>6.2857269606122097</v>
+      </c>
+      <c r="C50">
+        <v>-75.607147916904196</v>
+      </c>
+      <c r="D50" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8F3C82-B9B8-4684-AF65-B93CF2DDD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF55A1EB-1855-412C-9F53-665C059B8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6108" yWindow="3744" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="61">
   <si>
     <t>address</t>
   </si>
@@ -344,7 +344,44 @@
     <t>CL 49 A 78 A 39</t>
   </si>
   <si>
-    <t>CR 115 A 64 CC 4</t>
+    <r>
+      <t>CL 5 S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 25 233</t>
+    </r>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>MEDELLIN</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
   </si>
 </sst>
 </file>
@@ -764,17 +801,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -787,8 +825,11 @@
       <c r="D1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -801,8 +842,11 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -815,8 +859,11 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -829,8 +876,11 @@
       <c r="D4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -843,8 +893,11 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -857,8 +910,11 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -871,8 +927,11 @@
       <c r="D7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -885,8 +944,11 @@
       <c r="D8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -899,8 +961,11 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -913,8 +978,11 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -927,8 +995,11 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -941,8 +1012,11 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -955,8 +1029,11 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -969,8 +1046,11 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -983,8 +1063,11 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -996,6 +1079,9 @@
       </c>
       <c r="D16" t="s">
         <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1011,6 +1097,9 @@
       <c r="D17" t="s">
         <v>11</v>
       </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1025,6 +1114,9 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1039,6 +1131,9 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1053,6 +1148,9 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1067,6 +1165,9 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1082,6 +1183,9 @@
       <c r="D22" t="s">
         <v>27</v>
       </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1096,6 +1200,9 @@
       <c r="D23" t="s">
         <v>27</v>
       </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1110,6 +1217,9 @@
       <c r="D24" t="s">
         <v>30</v>
       </c>
+      <c r="E24" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1124,6 +1234,9 @@
       <c r="D25" t="s">
         <v>30</v>
       </c>
+      <c r="E25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1138,6 +1251,9 @@
       <c r="D26" t="s">
         <v>30</v>
       </c>
+      <c r="E26" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1152,6 +1268,9 @@
       <c r="D27" t="s">
         <v>30</v>
       </c>
+      <c r="E27" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1166,6 +1285,9 @@
       <c r="D28" t="s">
         <v>30</v>
       </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1180,6 +1302,9 @@
       <c r="D29" t="s">
         <v>30</v>
       </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1194,6 +1319,9 @@
       <c r="D30" t="s">
         <v>30</v>
       </c>
+      <c r="E30" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1208,6 +1336,9 @@
       <c r="D31" t="s">
         <v>30</v>
       </c>
+      <c r="E31" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1222,8 +1353,11 @@
       <c r="D32" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1236,8 +1370,11 @@
       <c r="D33" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1250,10 +1387,13 @@
       <c r="D34" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B35" s="11">
         <v>6.1931741895951999</v>
@@ -1264,8 +1404,11 @@
       <c r="D35" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1279,8 +1422,11 @@
       <c r="D36" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1293,8 +1439,11 @@
       <c r="D37" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1307,8 +1456,11 @@
       <c r="D38" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1321,8 +1473,11 @@
       <c r="D39" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1335,8 +1490,11 @@
       <c r="D40" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1349,8 +1507,11 @@
       <c r="D41" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1363,8 +1524,11 @@
       <c r="D42" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1377,8 +1541,11 @@
       <c r="D43" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1391,8 +1558,11 @@
       <c r="D44" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1405,8 +1575,11 @@
       <c r="D45" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1419,8 +1592,11 @@
       <c r="D46" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1433,8 +1609,11 @@
       <c r="D47" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1447,8 +1626,11 @@
       <c r="D48" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1461,19 +1643,8 @@
       <c r="D49" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="10">
-        <v>6.2857269606122097</v>
-      </c>
-      <c r="C50">
-        <v>-75.607147916904196</v>
-      </c>
-      <c r="D50" t="s">
-        <v>53</v>
+      <c r="E49" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF55A1EB-1855-412C-9F53-665C059B8862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9BB05C-AD18-4A26-A5D1-AA25A8CDAAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,9 +335,6 @@
     <t>Bello</t>
   </si>
   <si>
-    <t>CR 67 B 51 A 72</t>
-  </si>
-  <si>
     <t>Colores</t>
   </si>
   <si>
@@ -382,6 +379,9 @@
   </si>
   <si>
     <t>BELLO</t>
+  </si>
+  <si>
+    <t>CR 67 B TV 51 A 72</t>
   </si>
 </sst>
 </file>
@@ -826,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -843,7 +843,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -860,7 +860,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -894,7 +894,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -911,7 +911,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -928,7 +928,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -945,7 +945,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -996,7 +996,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1013,7 +1013,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1030,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1047,7 +1047,7 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1064,7 +1064,7 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1081,7 +1081,7 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1098,7 +1098,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1115,7 +1115,7 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1132,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1149,7 +1149,7 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1166,7 +1166,7 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="9"/>
     </row>
@@ -1184,7 +1184,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1201,7 +1201,7 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1218,7 +1218,7 @@
         <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1235,7 +1235,7 @@
         <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1252,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1269,7 +1269,7 @@
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1286,7 +1286,7 @@
         <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1303,7 +1303,7 @@
         <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1320,7 +1320,7 @@
         <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1337,7 +1337,7 @@
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1354,7 +1354,7 @@
         <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1371,7 +1371,7 @@
         <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1388,12 +1388,12 @@
         <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B35" s="11">
         <v>6.1931741895951999</v>
@@ -1405,7 +1405,7 @@
         <v>30</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1423,7 +1423,7 @@
         <v>30</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1440,7 +1440,7 @@
         <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1457,7 +1457,7 @@
         <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1474,7 +1474,7 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1491,7 +1491,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1508,7 +1508,7 @@
         <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1525,7 +1525,7 @@
         <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
         <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1559,7 +1559,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1576,7 +1576,7 @@
         <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1593,12 +1593,12 @@
         <v>30</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>6.2584312600000001</v>
@@ -1607,15 +1607,15 @@
         <v>-75.583113519999998</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48">
         <v>6.2614499349999999</v>
@@ -1624,10 +1624,10 @@
         <v>-75.59603568</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1644,7 +1644,7 @@
         <v>51</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9BB05C-AD18-4A26-A5D1-AA25A8CDAAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2E394B-FFC7-489B-A8BD-76975873DE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
   <si>
     <t>address</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>CR 67 B TV 51 A 72</t>
+  </si>
+  <si>
+    <t>CR 115 A 64 CC 4</t>
   </si>
 </sst>
 </file>
@@ -801,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1647,6 +1650,23 @@
         <v>59</v>
       </c>
     </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50">
+        <v>6.2857269609999999</v>
+      </c>
+      <c r="C50">
+        <v>-75.607147920000003</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2E394B-FFC7-489B-A8BD-76975873DE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D409D6F-C1BB-49B2-8EDB-4CCFE1CFC6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$50</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
@@ -208,9 +211,6 @@
     <t>CR 80 B 8 SUR 36</t>
   </si>
   <si>
-    <t>CR 72 39 A 22</t>
-  </si>
-  <si>
     <t>TV 15 DG 79 240</t>
   </si>
   <si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>CR 115 A 64 CC 4</t>
+  </si>
+  <si>
+    <t>CR 72 TV 39 A 22</t>
   </si>
 </sst>
 </file>
@@ -829,7 +832,7 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -846,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -863,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -880,7 +883,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -897,7 +900,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -914,7 +917,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -931,7 +934,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -948,7 +951,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -965,7 +968,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,7 +985,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -999,7 +1002,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1016,12 +1019,12 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>6.24193607298439</v>
@@ -1033,12 +1036,12 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>6.2206541533742499</v>
@@ -1050,12 +1053,12 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>6.2360094759560099</v>
@@ -1067,12 +1070,12 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>6.2491252797273704</v>
@@ -1084,12 +1087,12 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>6.21363736416951</v>
@@ -1101,12 +1104,12 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>6.2014104380581596</v>
@@ -1118,12 +1121,12 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>6.2029779348074401</v>
@@ -1135,12 +1138,12 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>6.2193486483621996</v>
@@ -1152,12 +1155,12 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="6">
         <v>6.2055100000000003</v>
@@ -1169,13 +1172,13 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="8">
         <v>6.1506690819802801</v>
@@ -1184,15 +1187,15 @@
         <v>-75.605539089698993</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>6.1431049230803803</v>
@@ -1201,15 +1204,15 @@
         <v>-75.614027116736594</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="9">
         <v>6.2003656647582499</v>
@@ -1218,15 +1221,15 @@
         <v>-75.576072516427004</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25">
         <v>6.2012206869961499</v>
@@ -1235,15 +1238,15 @@
         <v>-75.577266796531006</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26">
         <v>6.1978684312551797</v>
@@ -1252,15 +1255,15 @@
         <v>-75.572815065978205</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>6.2054757571363997</v>
@@ -1269,15 +1272,15 @@
         <v>-75.575148760836896</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28">
         <v>6.2029440967304703</v>
@@ -1286,15 +1289,15 @@
         <v>-75.569805556183596</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29">
         <v>6.1998339078687801</v>
@@ -1303,15 +1306,15 @@
         <v>-75.562710064096905</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30">
         <v>6.2325358425078896</v>
@@ -1320,15 +1323,15 @@
         <v>-75.569802118212607</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="10">
         <v>6.2283366361338999</v>
@@ -1337,15 +1340,15 @@
         <v>-75.564789821177598</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="10">
         <v>6.2220457226222203</v>
@@ -1354,15 +1357,15 @@
         <v>-75.573503565057194</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="10">
         <v>6.1932089660288696</v>
@@ -1371,15 +1374,15 @@
         <v>-75.562406723559306</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="10">
         <v>6.2255598265081904</v>
@@ -1388,15 +1391,15 @@
         <v>-75.560795728534899</v>
       </c>
       <c r="D34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="11">
         <v>6.1931741895951999</v>
@@ -1405,15 +1408,15 @@
         <v>-75.5623997347966</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="13">
         <v>6.2343488581450099</v>
@@ -1423,15 +1426,15 @@
         <v>-75.536279561335206</v>
       </c>
       <c r="D36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37">
         <v>6.2202944163771496</v>
@@ -1440,15 +1443,15 @@
         <v>-75.574662687365702</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="2">
         <v>6.22431</v>
@@ -1457,15 +1460,15 @@
         <v>-75.561790000000002</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="13">
         <v>6.2220538043196596</v>
@@ -1474,15 +1477,15 @@
         <v>-75.5734705647412</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="13">
         <v>6.22560478153442</v>
@@ -1491,15 +1494,15 @@
         <v>-75.566973612531797</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41">
         <v>6.2218313180514802</v>
@@ -1508,15 +1511,15 @@
         <v>-75.574244689796203</v>
       </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>6.2255530668247303</v>
@@ -1525,15 +1528,15 @@
         <v>-75.562572653812296</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>6.1948689974301603</v>
@@ -1542,15 +1545,15 @@
         <v>-75.556969341093307</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>6.2255980917086404</v>
@@ -1559,15 +1562,15 @@
         <v>-75.566973298535501</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>6.1775180853905196</v>
@@ -1576,15 +1579,15 @@
         <v>-75.560908648002595</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>6.2006567972248199</v>
@@ -1593,15 +1596,15 @@
         <v>-75.573747976820798</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47">
         <v>6.2584312600000001</v>
@@ -1610,15 +1613,15 @@
         <v>-75.583113519999998</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>6.2614499349999999</v>
@@ -1627,15 +1630,15 @@
         <v>-75.59603568</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="10">
         <v>6.3260569198161596</v>
@@ -1644,15 +1647,15 @@
         <v>-75.565799612624602</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>6.2857269609999999</v>
@@ -1661,13 +1664,14 @@
         <v>-75.607147920000003</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D409D6F-C1BB-49B2-8EDB-4CCFE1CFC6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB660B2-3401-4FA2-96AE-6648ACEB3DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="68">
   <si>
     <t>address</t>
   </si>
@@ -388,6 +388,24 @@
   </si>
   <si>
     <t>CR 72 TV 39 A 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIR 72 39 A 22 </t>
+  </si>
+  <si>
+    <t>CR 79 19 A 56</t>
+  </si>
+  <si>
+    <t>Fontibon</t>
+  </si>
+  <si>
+    <t>BOGOTA</t>
+  </si>
+  <si>
+    <t>CR 78 16 D 48</t>
+  </si>
+  <si>
+    <t>CR 78 11C 21</t>
   </si>
 </sst>
 </file>
@@ -472,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -493,6 +511,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -807,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1670,6 +1689,74 @@
         <v>55</v>
       </c>
     </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B51">
+        <v>6.2420109590691597</v>
+      </c>
+      <c r="C51">
+        <v>-75.592732158026706</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52">
+        <v>4.6582179067126299</v>
+      </c>
+      <c r="C52">
+        <v>-74.127878303039793</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="14">
+        <v>4.6524956550000001</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-74.131747989999994</v>
+      </c>
+      <c r="D53" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54">
+        <v>4.6477517072108903</v>
+      </c>
+      <c r="C54">
+        <v>-74.135299360941005</v>
+      </c>
+      <c r="D54" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB660B2-3401-4FA2-96AE-6648ACEB3DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28816D6-90C5-44A2-A406-5590EE896CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="72">
   <si>
     <t>address</t>
   </si>
@@ -406,6 +406,18 @@
   </si>
   <si>
     <t>CR 78 11C 21</t>
+  </si>
+  <si>
+    <t>TV 65 A 32 56</t>
+  </si>
+  <si>
+    <t>Rionegro</t>
+  </si>
+  <si>
+    <t>RIONEGRO</t>
+  </si>
+  <si>
+    <t>CL 40 C 62 37</t>
   </si>
 </sst>
 </file>
@@ -826,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1757,6 +1769,40 @@
         <v>65</v>
       </c>
     </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55">
+        <v>6.1631142900986999</v>
+      </c>
+      <c r="C55">
+        <v>-75.358045659912193</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56">
+        <v>6.1469045556095798</v>
+      </c>
+      <c r="C56">
+        <v>-75.3846309162751</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28816D6-90C5-44A2-A406-5590EE896CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80389C3A-FA8A-4771-B70C-DE81C3A42C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="73">
   <si>
     <t>address</t>
   </si>
@@ -418,6 +418,9 @@
   </si>
   <si>
     <t>CL 40 C 62 37</t>
+  </si>
+  <si>
+    <t>CL 22 D 86 61</t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1720,47 +1723,47 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B52">
-        <v>4.6582179067126299</v>
+        <v>6.1631142900986999</v>
       </c>
       <c r="C52">
-        <v>-74.127878303039793</v>
+        <v>-75.358045659912193</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" s="14">
-        <v>4.6524956550000001</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-74.131747989999994</v>
+        <v>71</v>
+      </c>
+      <c r="B53">
+        <v>6.1469045556095798</v>
+      </c>
+      <c r="C53">
+        <v>-75.3846309162751</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E53" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>67</v>
+      <c r="A54" t="s">
+        <v>72</v>
       </c>
       <c r="B54">
-        <v>4.6477517072108903</v>
+        <v>4.6684605675795101</v>
       </c>
       <c r="C54">
-        <v>-74.135299360941005</v>
+        <v>-74.129166921494004</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -1771,36 +1774,53 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B55">
-        <v>6.1631142900986999</v>
+        <v>4.6582179067126299</v>
       </c>
       <c r="C55">
-        <v>-75.358045659912193</v>
+        <v>-74.127878303039793</v>
       </c>
       <c r="D55" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56">
-        <v>6.1469045556095798</v>
-      </c>
-      <c r="C56">
-        <v>-75.3846309162751</v>
+        <v>66</v>
+      </c>
+      <c r="B56" s="14">
+        <v>4.6524956550000001</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-74.131747989999994</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>70</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57">
+        <v>4.6477517072108903</v>
+      </c>
+      <c r="C57">
+        <v>-74.135299360941005</v>
+      </c>
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\GitHub\Inmuebles\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80389C3A-FA8A-4771-B70C-DE81C3A42C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90191477-6F92-447C-8BD4-997CEB1632CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$51</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
   <si>
     <t>address</t>
   </si>
@@ -421,6 +421,15 @@
   </si>
   <si>
     <t>CL 22 D 86 61</t>
+  </si>
+  <si>
+    <t>CR 9 A 20 SUR 40 </t>
+  </si>
+  <si>
+    <t>CL 27 08 44</t>
+  </si>
+  <si>
+    <t>LA CEJA</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1621,13 +1630,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B46">
-        <v>6.2006567972248199</v>
+        <v>6.1770535989385396</v>
       </c>
       <c r="C46">
-        <v>-75.573747976820798</v>
+        <v>-75.544752705749005</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -1638,16 +1647,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B47">
-        <v>6.2584312600000001</v>
+        <v>6.2006567972248199</v>
       </c>
       <c r="C47">
-        <v>-75.583113519999998</v>
+        <v>-75.573747976820798</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
@@ -1655,13 +1664,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B48">
-        <v>6.2614499349999999</v>
+        <v>6.2584312600000001</v>
       </c>
       <c r="C48">
-        <v>-75.59603568</v>
+        <v>-75.583113519999998</v>
       </c>
       <c r="D48" t="s">
         <v>51</v>
@@ -1672,50 +1681,50 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="10">
-        <v>6.3260569198161596</v>
+        <v>52</v>
+      </c>
+      <c r="B49">
+        <v>6.2614499349999999</v>
       </c>
       <c r="C49">
-        <v>-75.565799612624602</v>
+        <v>-75.59603568</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50">
-        <v>6.2857269609999999</v>
+        <v>49</v>
+      </c>
+      <c r="B50" s="10">
+        <v>6.3260569198161596</v>
       </c>
       <c r="C50">
-        <v>-75.607147920000003</v>
+        <v>-75.565799612624602</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B51">
-        <v>6.2420109590691597</v>
+        <v>6.2857269609999999</v>
       </c>
       <c r="C51">
-        <v>-75.592732158026706</v>
+        <v>-75.607147920000003</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
         <v>55</v>
@@ -1723,30 +1732,30 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B52">
-        <v>6.1631142900986999</v>
+        <v>6.2420109590691597</v>
       </c>
       <c r="C52">
-        <v>-75.358045659912193</v>
+        <v>-75.592732158026706</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B53">
-        <v>6.1469045556095798</v>
+        <v>6.1631142900986999</v>
       </c>
       <c r="C53">
-        <v>-75.3846309162751</v>
+        <v>-75.358045659912193</v>
       </c>
       <c r="D53" t="s">
         <v>69</v>
@@ -1757,30 +1766,30 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54">
-        <v>4.6684605675795101</v>
+        <v>6.1469045556095798</v>
       </c>
       <c r="C54">
-        <v>-74.129166921494004</v>
+        <v>-75.3846309162751</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E54" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B55">
-        <v>4.6582179067126299</v>
+        <v>4.6684605675795101</v>
       </c>
       <c r="C55">
-        <v>-74.127878303039793</v>
+        <v>-74.129166921494004</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1791,13 +1800,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="14">
-        <v>4.6524956550000001</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-74.131747989999994</v>
+        <v>63</v>
+      </c>
+      <c r="B56">
+        <v>4.6582179067126299</v>
+      </c>
+      <c r="C56">
+        <v>-74.127878303039793</v>
       </c>
       <c r="D56" t="s">
         <v>64</v>
@@ -1807,14 +1816,14 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57">
-        <v>4.6477517072108903</v>
-      </c>
-      <c r="C57">
-        <v>-74.135299360941005</v>
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="14">
+        <v>4.6524956550000001</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-74.131747989999994</v>
       </c>
       <c r="D57" t="s">
         <v>64</v>
@@ -1823,8 +1832,42 @@
         <v>65</v>
       </c>
     </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58">
+        <v>4.6477517072108903</v>
+      </c>
+      <c r="C58">
+        <v>-74.135299360941005</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59">
+        <v>6.0346158880000003</v>
+      </c>
+      <c r="C59">
+        <v>-75.418951509999999</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\GitHub\Inmuebles\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90191477-6F92-447C-8BD4-997CEB1632CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661D5CD1-2322-4AB0-BEA9-06F638F2F701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="75">
   <si>
     <t>address</t>
   </si>
@@ -423,13 +423,10 @@
     <t>CL 22 D 86 61</t>
   </si>
   <si>
-    <t>CR 9 A 20 SUR 40 </t>
-  </si>
-  <si>
-    <t>CL 27 08 44</t>
-  </si>
-  <si>
-    <t>LA CEJA</t>
+    <t xml:space="preserve">DG 55A 18 47 </t>
+  </si>
+  <si>
+    <t>CR 86 48 A 142</t>
   </si>
 </sst>
 </file>
@@ -850,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1630,13 +1627,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B46">
-        <v>6.1770535989385396</v>
+        <v>6.1770429703628498</v>
       </c>
       <c r="C46">
-        <v>-75.544752705749005</v>
+        <v>-75.544755760218905</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -1749,47 +1746,47 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B53">
-        <v>6.1631142900986999</v>
+        <v>4.6684605675795101</v>
       </c>
       <c r="C53">
-        <v>-75.358045659912193</v>
+        <v>-74.129166921494004</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B54">
-        <v>6.1469045556095798</v>
+        <v>4.6582179067126299</v>
       </c>
       <c r="C54">
-        <v>-75.3846309162751</v>
+        <v>-74.127878303039793</v>
       </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>72</v>
-      </c>
-      <c r="B55">
-        <v>4.6684605675795101</v>
-      </c>
-      <c r="C55">
-        <v>-74.129166921494004</v>
+        <v>66</v>
+      </c>
+      <c r="B55" s="14">
+        <v>4.6524956550000001</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-74.131747989999994</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1799,14 +1796,14 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>63</v>
+      <c r="A56" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="B56">
-        <v>4.6582179067126299</v>
+        <v>4.6477517072108903</v>
       </c>
       <c r="C56">
-        <v>-74.127878303039793</v>
+        <v>-74.135299360941005</v>
       </c>
       <c r="D56" t="s">
         <v>64</v>
@@ -1817,53 +1814,70 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="14">
-        <v>4.6524956550000001</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-74.131747989999994</v>
+        <v>73</v>
+      </c>
+      <c r="B57">
+        <v>6.1259963210239796</v>
+      </c>
+      <c r="C57">
+        <v>-75.379807255480301</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E57" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
-        <v>67</v>
+      <c r="A58" t="s">
+        <v>68</v>
       </c>
       <c r="B58">
-        <v>4.6477517072108903</v>
+        <v>6.1631142900986999</v>
       </c>
       <c r="C58">
-        <v>-74.135299360941005</v>
+        <v>-75.358045659912193</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E58" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B59">
-        <v>6.0346158880000003</v>
+        <v>6.1469045556095798</v>
       </c>
       <c r="C59">
-        <v>-75.418951509999999</v>
+        <v>-75.3846309162751</v>
       </c>
       <c r="D59" t="s">
         <v>69</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60">
+        <v>6.1533687984480201</v>
+      </c>
+      <c r="C60">
+        <v>-75.397360713942604</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661D5CD1-2322-4AB0-BEA9-06F638F2F701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801605AD-2C53-45D5-B30C-AF35AA99B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="76">
   <si>
     <t>address</t>
   </si>
@@ -428,6 +428,9 @@
   <si>
     <t>CR 86 48 A 142</t>
   </si>
+  <si>
+    <t>CR 78 16 D 71</t>
+  </si>
 </sst>
 </file>
 
@@ -443,7 +446,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.000000"/>
     <numFmt numFmtId="171" formatCode="#,##0.00000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,6 +493,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -511,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -533,6 +541,7 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -847,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1880,6 +1889,23 @@
         <v>70</v>
       </c>
     </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61">
+        <v>4.6504631008714901</v>
+      </c>
+      <c r="C61">
+        <v>-74.131622197927896</v>
+      </c>
+      <c r="D61" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801605AD-2C53-45D5-B30C-AF35AA99B60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3422958-7B15-42D6-9D2B-8D3ED939E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="79">
   <si>
     <t>address</t>
   </si>
@@ -430,6 +430,15 @@
   </si>
   <si>
     <t>CR 78 16 D 71</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>CL 34 34 C 165</t>
+  </si>
+  <si>
+    <t>CL 12 SUR 22 121</t>
   </si>
 </sst>
 </file>
@@ -856,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1906,6 +1915,40 @@
         <v>65</v>
       </c>
     </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62">
+        <v>6.2336960837475202</v>
+      </c>
+      <c r="C62">
+        <v>-75.562905092936802</v>
+      </c>
+      <c r="D62" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="14">
+        <v>6.1863891994172899</v>
+      </c>
+      <c r="C63">
+        <v>-75.560767939002105</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Localizaciones.corr.xlsx
+++ b/data/Localizaciones.corr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3422958-7B15-42D6-9D2B-8D3ED939E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32BAE22-BCD7-4102-8368-225F10E8E5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="81">
   <si>
     <t>address</t>
   </si>
@@ -439,6 +439,12 @@
   </si>
   <si>
     <t>CL 12 SUR 22 121</t>
+  </si>
+  <si>
+    <t>CR 5 26 75</t>
+  </si>
+  <si>
+    <t>FUNZA</t>
   </si>
 </sst>
 </file>
@@ -865,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1949,6 +1955,23 @@
         <v>55</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64">
+        <v>4.7127501114851604</v>
+      </c>
+      <c r="C64">
+        <v>-74.196737981595106</v>
+      </c>
+      <c r="D64" t="s">
+        <v>64</v>
+      </c>
+      <c r="E64" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
